--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000207</v>
+        <v>115000208</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.26</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>13  19  23  35  38</t>
+          <t>02  03  07  25  33</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
@@ -1354,201 +1354,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.08.06</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>02  07  08  20  26  33</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000208</v>
+        <v>115000209</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  03  07  25  33</t>
+          <t>02  04  09  12  36</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.08.07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>02  12  19  21  25  41</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000209</v>
+        <v>115000210</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.08.29</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  04  09  12  36</t>
+          <t>03  06  17  23  33</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000210</v>
+        <v>115000211</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.29</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  06  17  23  33</t>
+          <t>05  10  12  33  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
@@ -1354,196 +1354,196 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000211</v>
+        <v>115000212</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  10  12  33  39</t>
+          <t>02  04  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000212</v>
+        <v>115000213</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  30  38</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000183</v>
+        <v>115000213</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.29</t>
+          <t>115.09.02</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  14  32  33  36</t>
+          <t>07  08  13  16  18</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000184</v>
+        <v>115000214</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  07  08  16  38</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000185</v>
+        <v>115000215</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  09  12  25  26</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000186</v>
+        <v>115000216</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.01</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  11  18  22  29</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000187</v>
+        <v>115000217</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  21  23  28  35</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000188</v>
+        <v>115000218</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>09  32  35  37  39</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000189</v>
+        <v>115000219</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.05</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  04  22  25  29</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000190</v>
+        <v>115000220</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  09  16  24  35</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000191</v>
+        <v>115000221</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  11  12  13  19</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000192</v>
+        <v>115000222</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.08</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  11  24  31  32</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
@@ -1354,36 +1354,36 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000054</v>
+        <v>115000064</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.06</t>
+          <t>115.08.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  12  15  24  30  31</t>
+          <t>11  25  28  30  31  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000055</v>
+        <v>115000065</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.09</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>10  22  24  29  35  37</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,161 +1394,161 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000056</v>
+        <v>115000066</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>11  24  29  32  35  38</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000057</v>
+        <v>115000067</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.16</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>17  23  25  29  34  36</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000058</v>
+        <v>115000068</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  12  13  23  29  31</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000059</v>
+        <v>115000069</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.23</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  10  13  21  29  31</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000060</v>
+        <v>115000070</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>19  22  28  31  33  35</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000061</v>
+        <v>115000071</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.30</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  14  17  19  21  23</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000062</v>
+        <v>115000072</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  15  22  26  34  36</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000063</v>
+        <v>115000073</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.06</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  07  08  20  26  33</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000068</v>
+        <v>115000078</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.07.07</t>
+          <t>115.08.11</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  13  15  18  19  42</t>
+          <t>08  12  16  24  29  46</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000069</v>
+        <v>115000079</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.07.10</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  04  15  18  29  49</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000070</v>
+        <v>115000080</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.07.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  25  34  36  45  46</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000071</v>
+        <v>115000081</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.07.17</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  06  12  14  17  26</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000072</v>
+        <v>115000082</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.07.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  08  15  26  35  46</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000073</v>
+        <v>115000083</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.07.24</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  15  27  34  35  44</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000074</v>
+        <v>115000084</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.07.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  19  24  26  32  43</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000075</v>
+        <v>115000085</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.07.31</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11  20  23  33  34  44</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000076</v>
+        <v>115000086</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.08.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  09  15  30  36  49</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000077</v>
+        <v>115000087</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.08.07</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  12  19  21  25  41</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>09/02(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  4  6</t>
+          <t>6  0  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>09/03(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2  8  5</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>09/04(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  3  9</t>
+          <t>2  9  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  6  6</t>
+          <t>0  6  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  9  1</t>
+          <t>4  8  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  9  1</t>
+          <t>7  7  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  1  5</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  0  7</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>9  6  9</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2  1  9</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07/29(三)</t>
+          <t>09/02(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  6  8  5</t>
+          <t>4  9  1  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07/30(四)</t>
+          <t>09/03(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2  9  3  1</t>
+          <t>6  1  2  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/31(五)</t>
+          <t>09/04(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  8</t>
+          <t>9  5  0  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08/01(六)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  1  9  5</t>
+          <t>1  6  6  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08/03(一)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  0  1  6</t>
+          <t>1  9  8  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08/04(二)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  8  4  3</t>
+          <t>2  2  1  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>08/05(三)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  8  2  3</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>08/06(四)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  3  4  5</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/07(五)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  1  9  3</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/08(六)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  6  2  4</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000213</v>
+        <v>115000214</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.02</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  08  13  16  18</t>
+          <t>18  19  22  23  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
@@ -1354,176 +1354,176 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.10</t>
+          <t>115.08.13</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>11  25  28  30  31  36</t>
+          <t>01  03  04  07  10  19</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1534,21 +1534,21 @@
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/02(三)</t>
+          <t>09/03(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>6  0  3</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/03(四)</t>
+          <t>09/04(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>2  9  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/04(五)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2  9  1</t>
+          <t>0  6  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0  6  6</t>
+          <t>4  8  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  8  7</t>
+          <t>7  7  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  7  0</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/02(三)</t>
+          <t>09/03(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  9</t>
+          <t>6  1  2  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/03(四)</t>
+          <t>09/04(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  1  2  9</t>
+          <t>9  5  0  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/04(五)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  5  0  9</t>
+          <t>1  6  6  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  6  6  3</t>
+          <t>1  9  8  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  9  8  9</t>
+          <t>2  2  1  4</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2  2  1  4</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000214</v>
+        <v>115000215</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>18  19  22  23  34</t>
+          <t>02  04  15  17  24</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.11</t>
+          <t>115.08.14</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  12  16  24  29  46</t>
+          <t>05  12  25  33  34  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/03(四)</t>
+          <t>09/04(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>2  9  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/04(五)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2  9  1</t>
+          <t>0  6  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>0  6  6</t>
+          <t>4  8  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  8  7</t>
+          <t>7  7  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  7  0</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/03(四)</t>
+          <t>09/04(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  1  2  9</t>
+          <t>9  5  0  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/04(五)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  5  0  9</t>
+          <t>1  6  6  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  6  6  3</t>
+          <t>1  9  8  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  9  8  9</t>
+          <t>2  2  1  4</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  2  1  4</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000215</v>
+        <v>115000216</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.05</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  04  15  17  24</t>
+          <t>03  08  10  28  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/04(五)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2  9  1</t>
+          <t>0  6  6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  6  6</t>
+          <t>4  8  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  8  7</t>
+          <t>7  7  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  7  0</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/04(五)</t>
+          <t>09/05(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  5  0  9</t>
+          <t>1  6  6  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  6  6  3</t>
+          <t>1  9  8  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  9  8  9</t>
+          <t>2  2  1  4</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2  2  1  4</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000216</v>
+        <v>115000217</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.05</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  08  10  28  38</t>
+          <t>19  25  26  31  35</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
@@ -1354,156 +1354,156 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.13</t>
+          <t>115.08.17</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  03  04  07  10  19</t>
+          <t>05  11  18  19  35  38</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1514,41 +1514,41 @@
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  6  6</t>
+          <t>4  8  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  8  7</t>
+          <t>7  7  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  7  0</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/05(六)</t>
+          <t>09/07(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  6  6  3</t>
+          <t>1  9  8  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  9  8  9</t>
+          <t>2  2  1  4</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2  2  1  4</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000217</v>
+        <v>115000218</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>19  25  26  31  35</t>
+          <t>03  07  25  29  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.14</t>
+          <t>115.08.18</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  12  25  33  34  35</t>
+          <t>01  14  25  27  29  43</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  8  7</t>
+          <t>7  7  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  7  0</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/07(一)</t>
+          <t>09/08(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  9  8  9</t>
+          <t>2  2  1  4</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2  2  1  4</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000218</v>
+        <v>115000219</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.09</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  07  25  29  30</t>
+          <t>05  06  08  28  29</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  7  0</t>
+          <t>7  7  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/08(二)</t>
+          <t>09/09(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2  2  1  4</t>
+          <t>5  0  8  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000219</v>
+        <v>115000220</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.09</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  06  08  28  29</t>
+          <t>04  14  30  35  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
@@ -1354,136 +1354,136 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.17</t>
+          <t>115.08.20</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  11  18  19  35  38</t>
+          <t>01  02  09  11  29  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1494,61 +1494,61 @@
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  7  3</t>
+          <t>9  9  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/09(三)</t>
+          <t>09/10(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  0  8  8</t>
+          <t>7  3  9  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000220</v>
+        <v>115000221</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  14  30  35  38</t>
+          <t>12  15  23  25  27</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.18</t>
+          <t>115.08.21</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  14  25  27  29  43</t>
+          <t>08  14  23  24  26  47</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>9  9  2</t>
+          <t>0  7  4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/10(四)</t>
+          <t>09/11(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  3  9  5</t>
+          <t>8  1  0  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000221</v>
+        <v>115000222</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.12</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>12  15  23  25  27</t>
+          <t>06  17  24  25  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  7  4</t>
+          <t>4  5  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/11(五)</t>
+          <t>09/12(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8  1  0  7</t>
+          <t>6  7  5  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000222</v>
+        <v>115000223</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.12</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  17  24  25  30</t>
+          <t>01  15  32  34  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
@@ -1354,116 +1354,116 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.20</t>
+          <t>115.08.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  02  09  11  29  35</t>
+          <t>06  07  09  23  26  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1474,81 +1474,81 @@
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  5  3</t>
+          <t>8  4  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/12(六)</t>
+          <t>09/14(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  7  5  8</t>
+          <t>8  5  6  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000223</v>
+        <v>115000224</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  15  32  34  39</t>
+          <t>04  12  23  26  31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.21</t>
+          <t>115.08.25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  14  23  24  26  47</t>
+          <t>12  24  26  32  35  40</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  4  9</t>
+          <t>7  0  4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/14(一)</t>
+          <t>09/15(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8  5  6  9</t>
+          <t>0  5  6  4</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000224</v>
+        <v>115000225</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.16</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  12  23  26  31</t>
+          <t>07  08  12  13  19</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  0  4</t>
+          <t>4  0  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/15(二)</t>
+          <t>09/16(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  5  6  4</t>
+          <t>4  6  4  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000225</v>
+        <v>115000226</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.16</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  08  12  13  19</t>
+          <t>02  08  11  12  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
@@ -1354,96 +1354,96 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.24</t>
+          <t>115.08.27</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  07  09  23  26  36</t>
+          <t>02  07  09  11  24  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.08.31</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>04  08  12  19  32  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1454,96 +1454,96 @@
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  0  0</t>
+          <t>4  9  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/16(三)</t>
+          <t>09/17(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4  6  4  1</t>
+          <t>6  4  9  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000226</v>
+        <v>115000227</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  08  11  12  34</t>
+          <t>02  03  06  24  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.25</t>
+          <t>115.08.28</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>12  24  26  32  35  40</t>
+          <t>09  20  23  26  36  44</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  9  8</t>
+          <t>1  4  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/17(四)</t>
+          <t>09/18(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  4  9  6</t>
+          <t>7  9  7  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000227</v>
+        <v>115000228</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.19</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  03  06  24  34</t>
+          <t>02  17  27  29  35</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  4  2</t>
+          <t>5  2  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/18(五)</t>
+          <t>09/19(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  9  7  6</t>
+          <t>4  2  3  2</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000228</v>
+        <v>115000229</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.19</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  17  27  29  35</t>
+          <t>04  20  22  30  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
@@ -1354,36 +1354,36 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000069</v>
+        <v>115000071</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.27</t>
+          <t>115.09.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  11  24  36</t>
+          <t>01  06  07  19  30  33</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000070</v>
+        <v>115000072</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.08.31</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  08  12  19  32  37</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,163 +1394,149 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000071</v>
+        <v>115000073</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000072</v>
+        <v>115000074</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000073</v>
+        <v>115000075</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000074</v>
+        <v>115000076</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000075</v>
+        <v>115000077</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000076</v>
+        <v>115000078</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000077</v>
+        <v>115000079</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n">
-        <v>115000078</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>115.09.28</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>01  02  04  17  29  34</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -1789,203 +1775,189 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.08.28</t>
+          <t>115.09.01</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>09  20  23  26  36  44</t>
+          <t>10  16  19  26  29  48</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n">
-        <v>115000092</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>115.09.29</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>01  02  04  13  30  38</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -2214,120 +2186,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  2  1</t>
+          <t>3  9  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2532,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/19(六)</t>
+          <t>09/21(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4  2  3  2</t>
+          <t>0  7  1  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2617,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000229</v>
+        <v>115000230</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  20  22  30  38</t>
+          <t>08  13  20  31  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
@@ -1954,10 +1954,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000093</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.10.02</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>04  14  20  26  40  47</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -2186,120 +2200,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  9  0</t>
+          <t>0  2  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
@@ -2532,84 +2546,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/21(一)</t>
+          <t>09/22(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  7  1  9</t>
+          <t>8  2  8  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2617,36 +2631,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000230</v>
+        <v>115000231</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.23</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  13  20  31  34</t>
+          <t>08  10  14  16  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
@@ -2200,120 +2200,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  2  3</t>
+          <t>0  6  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
@@ -2546,84 +2546,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/22(二)</t>
+          <t>09/23(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8  2  8  6</t>
+          <t>9  8  2  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2631,36 +2631,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000231</v>
+        <v>115000232</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.23</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  10  14  16  30</t>
+          <t>05  08  18  19  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,24 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="A11" s="4" t="n">
+        <v>115000080</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>115.10.05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>02  06  17  21  26  37</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
     </row>
     <row r="12"/>
     <row r="13"/>
@@ -2200,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>0  6  1</t>
+          <t>3  7  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
@@ -2546,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/23(三)</t>
+          <t>09/24(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  8  2  7</t>
+          <t>5  2  3  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2631,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000232</v>
+        <v>115000233</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  08  18  19  30</t>
+          <t>06  15  20  30  33</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.01</t>
+          <t>115.09.04</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>10  16  19  26  29  48</t>
+          <t>03  13  17  18  27  37</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  7  9</t>
+          <t>3  2  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/24(四)</t>
+          <t>09/25(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  3</t>
+          <t>7  7  9  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000233</v>
+        <v>115000234</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.26</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  15  20  30  33</t>
+          <t>17  18  30  34  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  2  9</t>
+          <t>3  5  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/25(五)</t>
+          <t>09/26(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  7  9  8</t>
+          <t>1  4  7  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000234</v>
+        <v>115000235</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.26</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>17  18  30  34  39</t>
+          <t>13  19  21  27  32</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
@@ -1354,36 +1354,36 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.03</t>
+          <t>115.09.07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  06  07  19  30  33</t>
+          <t>07  14  17  22  29  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,96 +1394,96 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1494,61 +1494,61 @@
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  5  9</t>
+          <t>3  3  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/26(六)</t>
+          <t>09/28(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  4  7  7</t>
+          <t>9  2  0  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000235</v>
+        <v>115000236</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>13  19  21  27  32</t>
+          <t>06  13  17  26  28</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.04</t>
+          <t>115.09.08</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  13  17  18  27  37</t>
+          <t>03  15  28  35  47  49</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  3  8</t>
+          <t>8  9  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/28(一)</t>
+          <t>09/29(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  2  0  9</t>
+          <t>2  9  4  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000236</v>
+        <v>115000237</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.09.30</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  13  17  26  28</t>
+          <t>02  07  09  14  33</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>8  9  1</t>
+          <t>5  5  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/29(二)</t>
+          <t>09/30(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2  9  4  6</t>
+          <t>4  4  1  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000237</v>
+        <v>115000238</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.30</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  07  09  14  33</t>
+          <t>01  03  16  28  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.07</t>
+          <t>115.09.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>07  14  17  22  29  35</t>
+          <t>08  17  18  29  33  38</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,96 +1374,96 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1474,81 +1474,81 @@
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  23  27  28  29  38</t>
+          <t>03  05  20  22  26  32</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  5  7</t>
+          <t>5  4  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/30(三)</t>
+          <t>10/01(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4  4  1  3</t>
+          <t>5  2  3  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000238</v>
+        <v>115000239</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  03  16  28  38</t>
+          <t>13  24  30  34  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.08</t>
+          <t>115.09.11</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  15  28  35  47  49</t>
+          <t>12  15  19  27  43  48</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  09  11  25  34  41</t>
+          <t>03  31  35  36  47  48</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>5  4  7</t>
+          <t>1  6  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/01(四)</t>
+          <t>10/02(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  2  3  9</t>
+          <t>5  9  7  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000239</v>
+        <v>115000240</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.03</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>13  24  30  34  38</t>
+          <t>05  28  29  33  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  6  0</t>
+          <t>3  3  2</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/02(五)</t>
+          <t>10/03(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  9  7  8</t>
+          <t>1  7  2  0</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000240</v>
+        <v>115000241</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.03</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  28  29  33  38</t>
+          <t>02  05  08  16  31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
@@ -1354,96 +1354,96 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.10</t>
+          <t>115.09.14</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>08  17  18  29  33  38</t>
+          <t>10  12  14  16  29  36</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1454,101 +1454,101 @@
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  23  27  28  29  38</t>
+          <t>03  05  20  22  26  32</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  05  20  22  26  32</t>
+          <t>06  12  18  25  30  33</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  3  2</t>
+          <t>7  9  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/03(六)</t>
+          <t>10/05(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  7  2  0</t>
+          <t>1  3  0  8</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000241</v>
+        <v>115000242</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  05  08  16  31</t>
+          <t>14  25  26  29  33</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.11</t>
+          <t>115.09.15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>12  15  19  27  43  48</t>
+          <t>02  03  18  21  22  39</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  09  11  25  34  41</t>
+          <t>03  31  35  36  47  48</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000096</v>
+        <v>115000097</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  31  35  36  47  48</t>
+          <t>06  15  21  40  43  49</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  9  0</t>
+          <t>2  5  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/05(一)</t>
+          <t>10/06(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  3  0  8</t>
+          <t>8  5  9  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000242</v>
+        <v>115000243</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>14  25  26  29  33</t>
+          <t>05  11  14  18  19</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2  5  7</t>
+          <t>4  8  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/06(二)</t>
+          <t>10/07(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8  5  9  1</t>
+          <t>6  4  6  2</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000243</v>
+        <v>115000244</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.07</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  11  14  18  19</t>
+          <t>03  07  15  17  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
@@ -1354,76 +1354,76 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.14</t>
+          <t>115.09.17</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>10  12  14  16  29  36</t>
+          <t>23  26  27  28  31  37</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1434,121 +1434,121 @@
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  23  27  28  29  38</t>
+          <t>03  05  20  22  26  32</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  05  20  22  26  32</t>
+          <t>06  12  18  25  30  33</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  12  18  25  30  33</t>
+          <t>09  10  21  24  27  36</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  8  1</t>
+          <t>3  2  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/07(三)</t>
+          <t>10/08(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6  4  6  2</t>
+          <t>3  3  3  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000244</v>
+        <v>115000245</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  07  15  17  30</t>
+          <t>20  23  25  27  31</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.15</t>
+          <t>115.09.18</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  03  18  21  22  39</t>
+          <t>01  06  14  21  31  35</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  09  11  25  34  41</t>
+          <t>03  31  35  36  47  48</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000096</v>
+        <v>115000097</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  31  35  36  47  48</t>
+          <t>06  15  21  40  43  49</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000097</v>
+        <v>115000098</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  15  21  40  43  49</t>
+          <t>02  05  19  33  40  43</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  2  0</t>
+          <t>3  9  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/08(四)</t>
+          <t>10/09(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3  3  3  9</t>
+          <t>5  1  9  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000245</v>
+        <v>115000246</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.10</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>20  23  25  27  31</t>
+          <t>14  21  23  32  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  9  1</t>
+          <t>9  1  7</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/09(五)</t>
+          <t>10/10(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5  1  9  6</t>
+          <t>3  8  8  3</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000246</v>
+        <v>115000247</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.10</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>14  21  23  32  34</t>
+          <t>06  16  24  36  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
@@ -1354,56 +1354,56 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.17</t>
+          <t>115.09.21</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>23  26  27  28  31  37</t>
+          <t>03  08  17  24  25  37</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1414,141 +1414,141 @@
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  23  27  28  29  38</t>
+          <t>03  05  20  22  26  32</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  05  20  22  26  32</t>
+          <t>06  12  18  25  30  33</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  12  18  25  30  33</t>
+          <t>09  10  21  24  27  36</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  10  21  24  27  36</t>
+          <t>01  09  10  21  22  31</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>9  1  7</t>
+          <t>3  8  8</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/10(六)</t>
+          <t>10/12(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3  8  8  3</t>
+          <t>2  0  0  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000247</v>
+        <v>115000248</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>06  16  24  36  39</t>
+          <t>02  03  09  20  30</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.18</t>
+          <t>115.09.22</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  06  14  21  31  35</t>
+          <t>14  15  18  30  35  45</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  09  11  25  34  41</t>
+          <t>03  31  35  36  47  48</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000096</v>
+        <v>115000097</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  31  35  36  47  48</t>
+          <t>06  15  21  40  43  49</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000097</v>
+        <v>115000098</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  15  21  40  43  49</t>
+          <t>02  05  19  33  40  43</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000098</v>
+        <v>115000099</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  05  19  33  40  43</t>
+          <t>09  10  33  38  40  45</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>3  8  8</t>
+          <t>7  7  9</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/12(一)</t>
+          <t>10/13(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2  0  0  9</t>
+          <t>1  3  5  6</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000248</v>
+        <v>115000249</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.14</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>02  03  09  20  30</t>
+          <t>01  09  13  19  25</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000257</v>
+        <v>115000258</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.24</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>03  07  14  17  27</t>
+          <t>01  17  24  27  35</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  7  9</t>
+          <t>9  5  3</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5  5  1</t>
+          <t>6  3  6</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/13(二)</t>
+          <t>10/14(三)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  3  5  6</t>
+          <t>7  5  3  5</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  6  0  4</t>
+          <t>9  5  3  3</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000249</v>
+        <v>115000250</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.14</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>01  09  13  19  25</t>
+          <t>14  15  26  32  34</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000257</v>
+        <v>115000258</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.24</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>03  07  14  17  27</t>
+          <t>01  17  24  27  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000258</v>
+        <v>115000259</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.24</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  17  24  27  35</t>
+          <t>13  15  19  28  35</t>
         </is>
       </c>
     </row>
@@ -1354,36 +1354,36 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.21</t>
+          <t>115.09.24</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  08  17  24  25  37</t>
+          <t>03  08  25  27  30  31</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1394,161 +1394,161 @@
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  23  27  28  29  38</t>
+          <t>03  05  20  22  26  32</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  05  20  22  26  32</t>
+          <t>06  12  18  25  30  33</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  12  18  25  30  33</t>
+          <t>09  10  21  24  27  36</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>09  10  21  24  27  36</t>
+          <t>01  09  10  21  22  31</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  09  10  21  22  31</t>
+          <t>01  07  19  26  31  32</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>03</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>9  5  3</t>
+          <t>4  9  6</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5  5  1</t>
+          <t>6  3  6</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6  3  6</t>
+          <t>2  3  0</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/14(三)</t>
+          <t>10/15(四)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7  5  3  5</t>
+          <t>8  9  8  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  6  0  4</t>
+          <t>9  5  3  3</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>9  5  3  3</t>
+          <t>2  7  1  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000250</v>
+        <v>115000251</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>14  15  26  32  34</t>
+          <t>09  23  24  25  32</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000257</v>
+        <v>115000258</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.24</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>03  07  14  17  27</t>
+          <t>01  17  24  27  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000258</v>
+        <v>115000259</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.24</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  17  24  27  35</t>
+          <t>13  15  19  28  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000259</v>
+        <v>115000260</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.26</t>
+          <t>115.10.27</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>13  15  19  28  35</t>
+          <t>02  06  15  27  28</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.22</t>
+          <t>115.09.25</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>14  15  18  30  35  45</t>
+          <t>05  13  24  25  28  33</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  09  11  25  34  41</t>
+          <t>03  31  35  36  47  48</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000096</v>
+        <v>115000097</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  31  35  36  47  48</t>
+          <t>06  15  21  40  43  49</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000097</v>
+        <v>115000098</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>06  15  21  40  43  49</t>
+          <t>02  05  19  33  40  43</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000098</v>
+        <v>115000099</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  05  19  33  40  43</t>
+          <t>09  10  33  38  40  45</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000099</v>
+        <v>115000100</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.27</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>09  10  33  38  40  45</t>
+          <t>08  14  16  34  38  41</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>09</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>4  9  6</t>
+          <t>1  4  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5  5  1</t>
+          <t>6  3  6</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>6  3  6</t>
+          <t>2  3  0</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2  3  0</t>
+          <t>6  9  8</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/15(四)</t>
+          <t>10/16(五)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8  9  8  1</t>
+          <t>1  5  0  1</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  6  0  4</t>
+          <t>9  5  3  3</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>9  5  3  3</t>
+          <t>2  7  1  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2  7  1  4</t>
+          <t>7  4  3  6</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000251</v>
+        <v>115000252</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.17</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>09  23  24  25  32</t>
+          <t>10  20  26  32  39</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000257</v>
+        <v>115000258</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.24</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>03  07  14  17  27</t>
+          <t>01  17  24  27  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000258</v>
+        <v>115000259</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.24</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>01  17  24  27  35</t>
+          <t>13  15  19  28  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000259</v>
+        <v>115000260</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.26</t>
+          <t>115.10.27</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>13  15  19  28  35</t>
+          <t>02  06  15  27  28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000260</v>
+        <v>115000261</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.27</t>
+          <t>115.10.28</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  06  15  27  28</t>
+          <t>06  11  13  19  35</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>1  4  1</t>
+          <t>6  1  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>5  5  1</t>
+          <t>6  3  6</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>6  3  6</t>
+          <t>2  3  0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2  3  0</t>
+          <t>6  9  8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/27(二)</t>
+          <t>10/28(三)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6  9  8</t>
+          <t>4  7  4</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/16(五)</t>
+          <t>10/17(六)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1  5  0  1</t>
+          <t>0  4  5  7</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>7  6  0  4</t>
+          <t>9  5  3  3</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>9  5  3  3</t>
+          <t>2  7  1  4</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2  7  1  4</t>
+          <t>7  4  3  6</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/27(二)</t>
+          <t>10/28(三)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>7  4  3  6</t>
+          <t>4  5  8  0</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000252</v>
+        <v>115000253</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.17</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>10  20  26  32  39</t>
+          <t>04  12  16  22  36</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000257</v>
+        <v>115000258</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.24</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  07  14  17  27</t>
+          <t>01  17  24  27  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000258</v>
+        <v>115000259</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.24</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>01  17  24  27  35</t>
+          <t>13  15  19  28  35</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000259</v>
+        <v>115000260</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.26</t>
+          <t>115.10.27</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>13  15  19  28  35</t>
+          <t>02  06  15  27  28</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000260</v>
+        <v>115000261</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.27</t>
+          <t>115.10.28</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>02  06  15  27  28</t>
+          <t>06  11  13  19  35</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000261</v>
+        <v>115000262</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.28</t>
+          <t>115.10.29</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>06  11  13  19  35</t>
+          <t>02  11  14  21  22</t>
         </is>
       </c>
     </row>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.24</t>
+          <t>115.09.28</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>03  08  25  27  30  31</t>
+          <t>01  02  04  17  29  34</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -1374,181 +1374,181 @@
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.28</t>
+          <t>115.10.01</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  17  29  34</t>
+          <t>02  04  18  26  33  37</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.01</t>
+          <t>115.10.05</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>02  04  18  26  33  37</t>
+          <t>02  06  17  21  26  37</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.05</t>
+          <t>115.10.08</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>02  06  17  21  26  37</t>
+          <t>04  23  27  28  29  38</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.08</t>
+          <t>115.10.12</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>04  23  27  28  29  38</t>
+          <t>03  05  20  22  26  32</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.12</t>
+          <t>115.10.15</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  05  20  22  26  32</t>
+          <t>06  12  18  25  30  33</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.15</t>
+          <t>115.10.19</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  12  18  25  30  33</t>
+          <t>09  10  21  24  27  36</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>09  10  21  24  27  36</t>
+          <t>01  09  10  21  22  31</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>01  09  10  21  22  31</t>
+          <t>01  07  19  26  31  32</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.26</t>
+          <t>115.10.29</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>01  07  19  26  31  32</t>
+          <t>03  06  11  16  26  37</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>6  1  1</t>
+          <t>7  6  1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5  5  1</t>
+          <t>6  3  6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>6  3  6</t>
+          <t>2  3  0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2  3  0</t>
+          <t>6  9  8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/27(二)</t>
+          <t>10/28(三)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>6  9  8</t>
+          <t>4  7  4</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/28(三)</t>
+          <t>10/29(四)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4  7  4</t>
+          <t>0  4  3</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/17(六)</t>
+          <t>10/19(一)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0  4  5  7</t>
+          <t>9  6  9  9</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7  6  0  4</t>
+          <t>9  5  3  3</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>9  5  3  3</t>
+          <t>2  7  1  4</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2  7  1  4</t>
+          <t>7  4  3  6</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/27(二)</t>
+          <t>10/28(三)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>7  4  3  6</t>
+          <t>4  5  8  0</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/28(三)</t>
+          <t>10/29(四)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4  5  8  0</t>
+          <t>6  6  4  4</t>
         </is>
       </c>
     </row>

--- a/最新開獎紀錄.xlsx
+++ b/最新開獎紀錄.xlsx
@@ -968,151 +968,151 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000253</v>
+        <v>115000254</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.10.19</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>04  12  16  22  36</t>
+          <t>01  15  30  36  38</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000254</v>
+        <v>115000255</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.21</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  15  30  36  38</t>
+          <t>04  08  15  18  28</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000255</v>
+        <v>115000256</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.21</t>
+          <t>115.10.22</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  08  15  18  28</t>
+          <t>03  08  14  23  28</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000256</v>
+        <v>115000257</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.22</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>03  08  14  23  28</t>
+          <t>03  07  14  17  27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000257</v>
+        <v>115000258</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.24</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  07  14  17  27</t>
+          <t>01  17  24  27  35</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000258</v>
+        <v>115000259</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.24</t>
+          <t>115.10.26</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>01  17  24  27  35</t>
+          <t>13  15  19  28  35</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000259</v>
+        <v>115000260</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.26</t>
+          <t>115.10.27</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>13  15  19  28  35</t>
+          <t>02  06  15  27  28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000260</v>
+        <v>115000261</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.27</t>
+          <t>115.10.28</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  06  15  27  28</t>
+          <t>06  11  13  19  35</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000261</v>
+        <v>115000262</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.28</t>
+          <t>115.10.29</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>06  11  13  19  35</t>
+          <t>02  11  14  21  22</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000262</v>
+        <v>115000263</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.29</t>
+          <t>115.10.30</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>02  11  14  21  22</t>
+          <t>09  11  12  31  37</t>
         </is>
       </c>
     </row>
@@ -1789,201 +1789,201 @@
     </row>
     <row r="2" ht="20" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>115.09.25</t>
+          <t>115.09.29</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>05  13  24  25  28  33</t>
+          <t>01  02  04  13  30  38</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>115.09.29</t>
+          <t>115.10.02</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>01  02  04  13  30  38</t>
+          <t>04  14  20  26  40  47</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>115.10.02</t>
+          <t>115.10.06</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>04  14  20  26  40  47</t>
+          <t>04  06  20  32  36  39</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>115.10.06</t>
+          <t>115.10.09</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>04  06  20  32  36  39</t>
+          <t>03  09  11  25  34  41</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>115.10.09</t>
+          <t>115.10.13</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>03  09  11  25  34  41</t>
+          <t>03  31  35  36  47  48</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
-        <v>115000096</v>
+        <v>115000097</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>115.10.13</t>
+          <t>115.10.16</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>03  31  35  36  47  48</t>
+          <t>06  15  21  40  43  49</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
-        <v>115000097</v>
+        <v>115000098</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>115.10.16</t>
+          <t>115.10.20</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>06  15  21  40  43  49</t>
+          <t>02  05  19  33  40  43</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>06</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
-        <v>115000098</v>
+        <v>115000099</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>115.10.20</t>
+          <t>115.10.23</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>02  05  19  33  40  43</t>
+          <t>09  10  33  38  40  45</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
-        <v>115000099</v>
+        <v>115000100</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>115.10.23</t>
+          <t>115.10.27</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>09  10  33  38  40  45</t>
+          <t>08  14  16  34  38  41</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>09</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
-        <v>115000100</v>
+        <v>115000101</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>115.10.27</t>
+          <t>115.10.30</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>08  14  16  34  38  41</t>
+          <t>04  22  25  30  34  37</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -2214,120 +2214,120 @@
     <row r="2" ht="20.5" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>7  6  1</t>
+          <t>8  7  0</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20.5" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>8  7  0</t>
+          <t>5  5  6</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20.5" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5  5  6</t>
+          <t>0  7  3</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20.5" customHeight="1" s="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>0  7  3</t>
+          <t>5  5  1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20.5" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>5  5  1</t>
+          <t>6  3  6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20.5" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6  3  6</t>
+          <t>2  3  0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20.5" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2  3  0</t>
+          <t>6  9  8</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20.5" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>10/27(二)</t>
+          <t>10/28(三)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>6  9  8</t>
+          <t>4  7  4</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.5" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10/28(三)</t>
+          <t>10/29(四)</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>4  7  4</t>
+          <t>0  4  3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20.5" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>10/29(四)</t>
+          <t>10/30(五)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0  4  3</t>
+          <t>1  5  6</t>
         </is>
       </c>
     </row>
@@ -2560,84 +2560,84 @@
     <row r="2" s="5">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10/19(一)</t>
+          <t>10/20(二)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>9  6  9  9</t>
+          <t>7  7  5  2</t>
         </is>
       </c>
     </row>
     <row r="3" s="5">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>10/20(二)</t>
+          <t>10/21(三)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7  7  5  2</t>
+          <t>4  9  1  4</t>
         </is>
       </c>
     </row>
     <row r="4" s="5">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>10/21(三)</t>
+          <t>10/22(四)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4  9  1  4</t>
+          <t>9  1  2  6</t>
         </is>
       </c>
     </row>
     <row r="5" s="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10/22(四)</t>
+          <t>10/23(五)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>9  1  2  6</t>
+          <t>7  6  0  4</t>
         </is>
       </c>
     </row>
     <row r="6" s="5">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/23(五)</t>
+          <t>10/24(六)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>7  6  0  4</t>
+          <t>9  5  3  3</t>
         </is>
       </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/24(六)</t>
+          <t>10/26(一)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>9  5  3  3</t>
+          <t>2  7  1  4</t>
         </is>
       </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10/26(一)</t>
+          <t>10/27(二)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2  7  1  4</t>
+          <t>7  4  3  6</t>
         </is>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -2645,36 +2645,36 @@
     <row r="9" s="5">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10/27(二)</t>
+          <t>10/28(三)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>7  4  3  6</t>
+          <t>4  5  8  0</t>
         </is>
       </c>
     </row>
     <row r="10" s="5">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10/28(三)</t>
+          <t>10/29(四)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4  5  8  0</t>
+          <t>6  6  4  4</t>
         </is>
       </c>
     </row>
     <row r="11" s="5">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10/29(四)</t>
+          <t>10/30(五)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>6  6  4  4</t>
+          <t>9  1  1  9</t>
         </is>
       </c>
     </row>
